--- a/output/pdf_financials_xlsx/NBM.xlsx
+++ b/output/pdf_financials_xlsx/NBM.xlsx
@@ -1362,13 +1362,13 @@
         <v>1.504558</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.592566</v>
+        <v>-0.592566</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.089372</v>
+        <v>-1.089372</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2.064679</v>
+        <v>-2.064679</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-1.980749</v>
@@ -1410,19 +1410,19 @@
         <v>0.01585</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.109652</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02</v>
+        <v>-1.486854</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.574434</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.004</v>
+        <v>-0.825368</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.009116</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1667,28 +1667,28 @@
         <v>-2.333402</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.554826</v>
+        <v>-1.554826</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.7334270000000001</v>
+        <v>-0.7334270000000001</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.7872169999999999</v>
+        <v>-0.7872169999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.410684</v>
+        <v>-0.410684</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.504558</v>
+        <v>-1.504558</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.592566</v>
+        <v>-0.592566</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.089372</v>
+        <v>-1.089372</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>2.064679</v>
+        <v>-2.064679</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-1.980749</v>
@@ -1856,28 +1856,28 @@
         <v>-2.333402</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.554826</v>
+        <v>-1.554826</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.7334270000000001</v>
+        <v>-0.7334270000000001</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.7872169999999999</v>
+        <v>-0.7872169999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.410684</v>
+        <v>-0.410684</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.504558</v>
+        <v>-1.504558</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.592566</v>
+        <v>-0.592566</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.089372</v>
+        <v>-1.089372</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2.064679</v>
+        <v>-2.064679</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-1.980749</v>
@@ -2069,19 +2069,19 @@
         <v>8.974622999999999</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>11.1059</v>
+        <v>-11.1059</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>24.447567</v>
+        <v>-24.447567</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>39.36085</v>
+        <v>-39.36085</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.21368</v>
+        <v>-8.21368</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>37.61395</v>
+        <v>-37.61395</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>47.661675</v>
+        <v>-47.661675</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>54.4686</v>
+        <v>-54.4686</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>103.23395</v>
+        <v>-103.23395</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>-99.03745000000001</v>
@@ -2155,13 +2155,13 @@
         <v>1.504558</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.592566</v>
+        <v>-0.592566</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.089372</v>
+        <v>-1.089372</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>2.064679</v>
+        <v>-2.064679</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-1.980749</v>
@@ -2281,13 +2281,13 @@
         <v>1.507454</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.594228</v>
+        <v>-0.590904</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.089372</v>
+        <v>-1.089372</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.064679</v>
+        <v>-2.064679</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-1.878209</v>
@@ -2426,28 +2426,28 @@
         <v>-0.6746828352173373</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.654537201347974</v>
+        <v>197.345462798652</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.9645899046020584</v>
+        <v>199.0354100953979</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -6260,16 +6260,16 @@
         <v>0.730976</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.654305</v>
+        <v>2.076857</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.153486</v>
+        <v>3.243346</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.737429</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.069661</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -6284,31 +6284,31 @@
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.104571</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.897832</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.993711</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.733711</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.792453</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.605731</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.891949</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.280495</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>21.462165</v>
       </c>
     </row>
     <row r="93">
@@ -11074,7 +11074,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -12956,7 +12960,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -14400,7 +14408,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15892,7 +15904,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -17484,7 +17500,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -19062,7 +19082,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -20436,7 +20460,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21182,7 +21210,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -27086,7 +27118,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -64755,10 +64791,10 @@
         </is>
       </c>
       <c r="R532" s="5" t="n">
-        <v>2.064679</v>
+        <v>-2.064679</v>
       </c>
       <c r="S532" s="5" t="n">
-        <v>1.915222</v>
+        <v>-1.915222</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -66974,10 +67010,10 @@
         </is>
       </c>
       <c r="O553" s="5" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="P553" s="5" t="n">
-        <v>1.089372</v>
+        <v>-1.089372</v>
       </c>
       <c r="Q553" t="inlineStr">
         <is>
@@ -69059,10 +69095,10 @@
         </is>
       </c>
       <c r="N573" s="5" t="n">
-        <v>0.592566</v>
+        <v>-0.592566</v>
       </c>
       <c r="O573" s="5" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="P573" t="inlineStr">
         <is>
@@ -69273,10 +69309,10 @@
         </is>
       </c>
       <c r="N575" s="5" t="n">
-        <v>0.395641</v>
+        <v>-0.395641</v>
       </c>
       <c r="O575" s="5" t="n">
-        <v>3.812934</v>
+        <v>-3.812934</v>
       </c>
       <c r="P575" t="inlineStr">
         <is>
@@ -71011,16 +71047,16 @@
         </is>
       </c>
       <c r="J592" s="5" t="n">
-        <v>0.7334270000000001</v>
+        <v>-0.7334270000000001</v>
       </c>
       <c r="K592" s="5" t="n">
-        <v>0.7872169999999999</v>
+        <v>-0.7872169999999999</v>
       </c>
       <c r="L592" s="5" t="n">
-        <v>0.410684</v>
+        <v>-0.410684</v>
       </c>
       <c r="M592" s="5" t="n">
-        <v>1.504558</v>
+        <v>-1.504558</v>
       </c>
       <c r="N592" t="inlineStr">
         <is>
@@ -71217,16 +71253,16 @@
         </is>
       </c>
       <c r="J594" s="5" t="n">
-        <v>0.766577</v>
+        <v>-0.766577</v>
       </c>
       <c r="K594" s="5" t="n">
-        <v>0.7932169999999999</v>
+        <v>-0.7932169999999999</v>
       </c>
       <c r="L594" s="5" t="n">
-        <v>0.423259</v>
+        <v>-0.423259</v>
       </c>
       <c r="M594" s="5" t="n">
-        <v>1.504558</v>
+        <v>-1.504558</v>
       </c>
       <c r="N594" t="inlineStr">
         <is>
@@ -73106,10 +73142,10 @@
         </is>
       </c>
       <c r="I612" s="5" t="n">
-        <v>1.554826</v>
+        <v>-1.554826</v>
       </c>
       <c r="J612" s="5" t="n">
-        <v>0.7334270000000001</v>
+        <v>-0.7334270000000001</v>
       </c>
       <c r="K612" t="inlineStr">
         <is>
@@ -73318,10 +73354,10 @@
         </is>
       </c>
       <c r="I614" s="5" t="n">
-        <v>1.556374</v>
+        <v>-1.556374</v>
       </c>
       <c r="J614" s="5" t="n">
-        <v>0.766577</v>
+        <v>-0.766577</v>
       </c>
       <c r="K614" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NBM.xlsx
+++ b/output/pdf_financials_xlsx/NBM.xlsx
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.06725200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>-4.261507</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-10.206963</v>
+        <v>-10.274215</v>
       </c>
     </row>
     <row r="28">
@@ -2307,7 +2307,7 @@
         <v>-3.980283</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-9.852985</v>
+        <v>-9.920237</v>
       </c>
     </row>
     <row r="30">
@@ -8253,16 +8253,16 @@
         <v>0</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.050616</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.054725</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.083937</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.298438</v>
       </c>
     </row>
     <row r="125">
@@ -8316,16 +8316,16 @@
         <v>0</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.050616</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.054725</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.083937</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.298438</v>
       </c>
     </row>
     <row r="126">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -34082,7 +34082,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -58726,7 +58730,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -58836,7 +58840,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -59156,7 +59160,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -74180,7 +74184,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -75778,7 +75782,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">

--- a/output/pdf_financials_xlsx/NBM.xlsx
+++ b/output/pdf_financials_xlsx/NBM.xlsx
@@ -33472,7 +33472,11 @@
           <t>Additions to tangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33576,7 +33580,11 @@
           <t>Additions to intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -36344,7 +36352,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
